--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database (wip)/3. autonomous_db_owner (wip)/4. dml/3. user_area [18-20,29-35,10]/31. specialization_wip.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database (wip)/3. autonomous_db_owner (wip)/4. dml/3. user_area [18-20,29-35,10]/31. specialization_wip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\dml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D2FBDD-9ADF-4636-9878-8E5BF960CBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74668016-274E-408C-8E32-C85B84D9AF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="88">
   <si>
     <t>name</t>
   </si>
@@ -157,6 +157,138 @@
   </si>
   <si>
     <t>Program focused on verification, model checking, and correctness of software systems</t>
+  </si>
+  <si>
+    <t>92.5</t>
+  </si>
+  <si>
+    <t>87.4</t>
+  </si>
+  <si>
+    <t>91.8</t>
+  </si>
+  <si>
+    <t>85.6</t>
+  </si>
+  <si>
+    <t>97.6</t>
+  </si>
+  <si>
+    <t>96.1</t>
+  </si>
+  <si>
+    <t>97.1</t>
+  </si>
+  <si>
+    <t>96.4</t>
+  </si>
+  <si>
+    <t>90.8</t>
+  </si>
+  <si>
+    <t>93.2</t>
+  </si>
+  <si>
+    <t>92.7</t>
+  </si>
+  <si>
+    <t>95.1</t>
+  </si>
+  <si>
+    <t>98.2</t>
+  </si>
+  <si>
+    <t>91.4</t>
+  </si>
+  <si>
+    <t>96.8</t>
+  </si>
+  <si>
+    <t>94.5</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89.5</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>88.5</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>90.5</t>
+  </si>
+  <si>
+    <t>86.5</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>91.5</t>
+  </si>
+  <si>
+    <t>85.5</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>93.4</t>
+  </si>
+  <si>
+    <t>88.6</t>
+  </si>
+  <si>
+    <t>86.1</t>
+  </si>
+  <si>
+    <t>95.8</t>
+  </si>
+  <si>
+    <t>94.2</t>
+  </si>
+  <si>
+    <t>89.6</t>
+  </si>
+  <si>
+    <t>89.8</t>
   </si>
 </sst>
 </file>
@@ -192,11 +324,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,26 +671,26 @@
       <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2">
-        <v>92.5</v>
-      </c>
-      <c r="D2">
-        <v>92</v>
-      </c>
-      <c r="E2">
-        <v>89.5</v>
-      </c>
-      <c r="F2">
-        <v>82</v>
-      </c>
-      <c r="G2">
-        <v>88</v>
-      </c>
-      <c r="H2">
+      <c r="C2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="2">
         <v>97</v>
       </c>
-      <c r="I2">
-        <v>93.4</v>
+      <c r="I2" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>14</v>
@@ -576,26 +709,26 @@
       <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="C3">
-        <v>87.4</v>
-      </c>
-      <c r="D3">
-        <v>88.5</v>
-      </c>
-      <c r="E3">
-        <v>84</v>
-      </c>
-      <c r="F3">
-        <v>90</v>
-      </c>
-      <c r="G3">
-        <v>93</v>
-      </c>
-      <c r="H3">
-        <v>90.5</v>
-      </c>
-      <c r="I3">
-        <v>88.6</v>
+      <c r="C3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
@@ -614,26 +747,26 @@
       <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4">
-        <v>91.8</v>
-      </c>
-      <c r="D4">
-        <v>90</v>
-      </c>
-      <c r="E4">
-        <v>87</v>
-      </c>
-      <c r="F4">
-        <v>85</v>
-      </c>
-      <c r="G4">
-        <v>89</v>
-      </c>
-      <c r="H4">
+      <c r="C4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="2">
         <v>94</v>
       </c>
-      <c r="I4">
-        <v>90.8</v>
+      <c r="I4" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="J4" t="s">
         <v>21</v>
@@ -652,26 +785,26 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5">
-        <v>85.6</v>
-      </c>
-      <c r="D5">
-        <v>87</v>
-      </c>
-      <c r="E5">
+      <c r="C5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="2">
+        <v>88</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="F5">
-        <v>82</v>
-      </c>
-      <c r="G5">
-        <v>90</v>
-      </c>
-      <c r="H5">
-        <v>88</v>
-      </c>
-      <c r="I5">
-        <v>86.1</v>
       </c>
       <c r="J5" t="s">
         <v>29</v>
@@ -690,26 +823,26 @@
       <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6">
-        <v>97.6</v>
-      </c>
-      <c r="D6">
-        <v>94</v>
-      </c>
-      <c r="E6">
-        <v>92.5</v>
-      </c>
-      <c r="F6">
-        <v>88</v>
-      </c>
-      <c r="G6">
-        <v>90</v>
-      </c>
-      <c r="H6">
+      <c r="C6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="2">
         <v>99</v>
       </c>
-      <c r="I6">
-        <v>95.8</v>
+      <c r="I6" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="J6" t="s">
         <v>22</v>
@@ -728,26 +861,26 @@
       <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="C7">
-        <v>96.1</v>
-      </c>
-      <c r="D7">
-        <v>93</v>
-      </c>
-      <c r="E7">
-        <v>90</v>
-      </c>
-      <c r="F7">
-        <v>86</v>
-      </c>
-      <c r="G7">
-        <v>91</v>
-      </c>
-      <c r="H7">
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="2">
         <v>98</v>
       </c>
-      <c r="I7">
-        <v>94.2</v>
+      <c r="I7" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="J7" t="s">
         <v>23</v>
@@ -766,26 +899,26 @@
       <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="C8">
-        <v>97.1</v>
-      </c>
-      <c r="D8">
-        <v>92.5</v>
-      </c>
-      <c r="E8">
-        <v>91</v>
-      </c>
-      <c r="F8">
-        <v>87</v>
-      </c>
-      <c r="G8">
-        <v>89</v>
-      </c>
-      <c r="H8">
+      <c r="C8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="2">
         <v>98</v>
       </c>
-      <c r="I8">
-        <v>94.2</v>
+      <c r="I8" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="J8" t="s">
         <v>25</v>
@@ -804,26 +937,26 @@
       <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="C9">
-        <v>96.4</v>
-      </c>
-      <c r="D9">
-        <v>91</v>
-      </c>
-      <c r="E9">
-        <v>90.5</v>
-      </c>
-      <c r="F9">
-        <v>85</v>
-      </c>
-      <c r="G9">
-        <v>87</v>
-      </c>
-      <c r="H9">
+      <c r="C9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="2">
         <v>97</v>
       </c>
-      <c r="I9">
-        <v>93</v>
+      <c r="I9" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="J9" t="s">
         <v>36</v>
@@ -842,26 +975,26 @@
       <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="C10">
-        <v>90.8</v>
-      </c>
-      <c r="D10">
-        <v>89</v>
-      </c>
-      <c r="E10">
-        <v>86.5</v>
-      </c>
-      <c r="F10">
-        <v>88</v>
-      </c>
-      <c r="G10">
-        <v>92</v>
-      </c>
-      <c r="H10">
+      <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="2">
         <v>90</v>
       </c>
-      <c r="I10">
-        <v>89.6</v>
+      <c r="I10" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="J10" t="s">
         <v>37</v>
@@ -880,26 +1013,26 @@
       <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="C11">
-        <v>93.2</v>
-      </c>
-      <c r="D11">
-        <v>90</v>
-      </c>
-      <c r="E11">
-        <v>88</v>
-      </c>
-      <c r="F11">
-        <v>90</v>
-      </c>
-      <c r="G11">
-        <v>94</v>
-      </c>
-      <c r="H11">
+      <c r="C11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="2">
         <v>92</v>
       </c>
-      <c r="I11">
-        <v>91.4</v>
+      <c r="I11" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="J11" t="s">
         <v>38</v>
@@ -918,26 +1051,26 @@
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="C12">
-        <v>92.7</v>
-      </c>
-      <c r="D12">
-        <v>89.5</v>
-      </c>
-      <c r="E12">
-        <v>97</v>
-      </c>
-      <c r="F12">
-        <v>84</v>
-      </c>
-      <c r="G12">
-        <v>88</v>
-      </c>
-      <c r="H12">
+      <c r="C12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="2">
         <v>91</v>
       </c>
-      <c r="I12">
-        <v>89.8</v>
+      <c r="I12" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="J12" t="s">
         <v>39</v>
@@ -956,26 +1089,26 @@
       <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="C13">
-        <v>95.1</v>
-      </c>
-      <c r="D13">
-        <v>92</v>
-      </c>
-      <c r="E13">
-        <v>89</v>
-      </c>
-      <c r="F13">
-        <v>89</v>
-      </c>
-      <c r="G13">
-        <v>93</v>
-      </c>
-      <c r="H13">
+      <c r="C13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="2">
         <v>98</v>
       </c>
-      <c r="I13">
-        <v>94</v>
+      <c r="I13" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="J13" t="s">
         <v>40</v>
@@ -994,26 +1127,26 @@
       <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="C14">
-        <v>96.8</v>
-      </c>
-      <c r="D14">
-        <v>93</v>
-      </c>
-      <c r="E14">
-        <v>91.5</v>
-      </c>
-      <c r="F14">
-        <v>88</v>
-      </c>
-      <c r="G14">
-        <v>90</v>
-      </c>
-      <c r="H14">
+      <c r="C14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="2">
         <v>99</v>
       </c>
-      <c r="I14">
-        <v>95.1</v>
+      <c r="I14" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="J14" t="s">
         <v>41</v>
@@ -1032,26 +1165,26 @@
       <c r="B15" t="s">
         <v>18</v>
       </c>
-      <c r="C15">
-        <v>98.2</v>
-      </c>
-      <c r="D15">
-        <v>94.5</v>
-      </c>
-      <c r="E15">
-        <v>93</v>
-      </c>
-      <c r="F15">
-        <v>90</v>
-      </c>
-      <c r="G15">
-        <v>92</v>
-      </c>
-      <c r="H15">
+      <c r="C15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="2">
         <v>99</v>
       </c>
-      <c r="I15">
-        <v>96.4</v>
+      <c r="I15" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="J15" t="s">
         <v>42</v>
@@ -1070,26 +1203,26 @@
       <c r="B16" t="s">
         <v>18</v>
       </c>
-      <c r="C16">
-        <v>91.4</v>
-      </c>
-      <c r="D16">
-        <v>88</v>
-      </c>
-      <c r="E16">
-        <v>85.5</v>
-      </c>
-      <c r="F16">
-        <v>92</v>
-      </c>
-      <c r="G16">
-        <v>95</v>
-      </c>
-      <c r="H16">
+      <c r="C16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="2">
         <v>90</v>
       </c>
-      <c r="I16">
-        <v>89.8</v>
+      <c r="I16" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="J16" t="s">
         <v>43</v>
